--- a/research-repository/_index.xlsx
+++ b/research-repository/_index.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="355">
   <si>
     <t xml:space="preserve">HOW TO USE: Filter by Outcome, Primary Mechanism, Traffic Trajectory, AIO Portfolio Susceptibility, Dominant Content Model, Commercial Alignment, or AI Discoverability columns to find comps. Open Record File for full narrative and Calculation Log. Yellow = example row (delete before sharing with clients). Gray = formula-derived — do not edit manually. Source of truth: the markdown record. Correct the index from the record when they disagree.</t>
   </si>
@@ -93,6 +93,9 @@
     <t xml:space="preserve">Recovery Status</t>
   </si>
   <si>
+    <t xml:space="preserve">Observed Company Response</t>
+  </si>
+  <si>
     <t xml:space="preserve">Primary Mechanism</t>
   </si>
   <si>
@@ -201,6 +204,9 @@
     <t xml:space="preserve">None</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown</t>
+  </si>
+  <si>
     <t xml:space="preserve">AI-mediated informational demand erosion</t>
   </si>
   <si>
@@ -228,9 +234,6 @@
     <t xml:space="preserve">No</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ahrefs Export</t>
   </si>
   <si>
@@ -841,6 +844,69 @@
   </si>
   <si>
     <t xml:space="preserve">High — monthly performance file present; headline figures reproduced from source; position-bucket data directional only; Top Pages Gross Gain/Loss not usable without normalization cleanup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaunchDarkly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">launchdarkly.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Tools — Feature Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Ecosystem / B2B SaaS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Editorial-blog-led (post-consolidation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid-Market to Enterprise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V2.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Growth with mid-period pullback then 2026 acceleration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partial — real decline-and-recovery phase present within overall growth outcome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No intervention observed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical (structural consolidation candidate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High (Demand Expansion) / Medium (Technical)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not assessed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medium-High</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme single-page dependence (32.9% from /blog/deployment-strategies/); Homepage dependence (37.5%); International demand fragility (80% non-US on top page); Portfolio compression (−66.6% pages over study window); Limited page-specific authority on top non-branded page (UR 4, 10 RDs); AIO sustainability risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No (partial — single query only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahrefs SERP overview (single query — deployment strategies, US)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">company-records/launchdarkly.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">source-analyses/launchdarkly-v0.1.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaunchDarkly more than doubled organic traffic over two years through a decade-old educational page absorbing rising global search demand without a content rewrite; trajectory includes a real late-2025 pullback (−15%) coinciding with 66% portfolio compression, followed by demand-driven acceleration; AIO dual presence confirmed on primary keyword (cited, not displaced).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top non-branded page is 80% international — not representative for US-centric clients; extreme two-page concentration (70.4%) driven by demand expansion not replicable as an editorial strategy; portfolio compression mechanism unconfirmed; AIO click-suppression effect not separately assessed.</t>
   </si>
   <si>
     <t xml:space="preserve">Field Reference — Controlled Vocabulary</t>
@@ -1178,7 +1244,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1243,15 +1309,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1557,7 +1615,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AQ21"/>
+  <dimension ref="A1:AR22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
@@ -1767,25 +1825,28 @@
       <c r="AQ2" s="3" t="s">
         <v>43</v>
       </c>
+      <c r="AR2" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G3" s="5" t="n">
         <v>45658</v>
@@ -1802,16 +1863,16 @@
       </c>
       <c r="K3" s="5"/>
       <c r="L3" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P3" s="6" t="n">
         <v>-0.72</v>
@@ -1821,56 +1882,56 @@
         <v>Decline 50-75%</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="V3" s="4" t="s">
         <v>58</v>
       </c>
+      <c r="V3" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="W3" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="X3" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y3" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z3" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="AA3" s="1" t="s">
         <v>63</v>
       </c>
+      <c r="AA3" s="4" t="s">
+        <v>64</v>
+      </c>
       <c r="AB3" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AC3" s="6"/>
+        <v>65</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="AD3" s="6"/>
-      <c r="AE3" s="4" t="s">
-        <v>65</v>
-      </c>
+      <c r="AE3" s="6"/>
       <c r="AF3" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AG3" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AH3" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="AI3" s="4"/>
-      <c r="AJ3" s="4" t="s">
-        <v>68</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="AI3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ3" s="4"/>
       <c r="AK3" s="4" t="s">
         <v>69</v>
       </c>
@@ -1880,37 +1941,40 @@
       <c r="AM3" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="AN3" s="1" t="s">
+      <c r="AN3" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="AO3" s="4" t="s">
+      <c r="AO3" s="1" t="s">
         <v>73</v>
       </c>
       <c r="AP3" s="4" t="s">
         <v>74</v>
       </c>
       <c r="AQ3" s="4" t="s">
-        <v>60</v>
+        <v>75</v>
+      </c>
+      <c r="AR3" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G4" s="8" t="n">
         <v>45658</v>
@@ -1927,16 +1991,16 @@
       </c>
       <c r="K4" s="8"/>
       <c r="L4" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P4" s="10" t="n">
         <v>2.531</v>
@@ -1946,94 +2010,97 @@
         <v>Growth &gt;50%</v>
       </c>
       <c r="R4" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S4" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T4" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U4" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="V4" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7" t="s">
-        <v>60</v>
-      </c>
+      <c r="V4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="W4" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="X4" s="7"/>
       <c r="Y4" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z4" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA4" s="1" t="s">
         <v>63</v>
       </c>
+      <c r="AA4" s="7" t="s">
+        <v>62</v>
+      </c>
       <c r="AB4" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC4" s="10"/>
-      <c r="AD4" s="11"/>
-      <c r="AE4" s="7" t="s">
-        <v>85</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD4" s="10"/>
+      <c r="AE4" s="11"/>
       <c r="AF4" s="7" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="AG4" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AH4" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="AI4" s="7"/>
-      <c r="AJ4" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="AI4" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ4" s="7"/>
+      <c r="AK4" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="AL4" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="AK4" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL4" s="7" t="s">
-        <v>86</v>
-      </c>
       <c r="AM4" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="AN4" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="AO4" s="7" t="s">
         <v>87</v>
+      </c>
+      <c r="AN4" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="AO4" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="AP4" s="7" t="s">
         <v>88</v>
       </c>
       <c r="AQ4" s="7" t="s">
-        <v>60</v>
+        <v>89</v>
+      </c>
+      <c r="AR4" s="7" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>45658</v>
@@ -2050,16 +2117,16 @@
       </c>
       <c r="K5" s="13"/>
       <c r="L5" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M5" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N5" s="12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O5" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P5" s="14" t="n">
         <v>-0.424</v>
@@ -2069,98 +2136,101 @@
         <v>Decline 25-50%</v>
       </c>
       <c r="R5" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S5" s="12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="T5" s="12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U5" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="V5" s="12" t="s">
-        <v>95</v>
+        <v>58</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="W5" s="12" t="s">
         <v>96</v>
       </c>
       <c r="X5" s="12" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="Y5" s="12" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="Z5" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="AA5" s="1" t="s">
         <v>98</v>
+      </c>
+      <c r="AA5" s="12" t="s">
+        <v>64</v>
       </c>
       <c r="AB5" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="AC5" s="14" t="n">
+      <c r="AC5" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="AD5" s="14" t="n">
         <v>2.866</v>
       </c>
-      <c r="AD5" s="12"/>
-      <c r="AE5" s="12" t="s">
-        <v>100</v>
-      </c>
+      <c r="AE5" s="12"/>
       <c r="AF5" s="12" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="AG5" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AH5" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="AI5" s="12"/>
-      <c r="AJ5" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="AI5" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ5" s="12"/>
+      <c r="AK5" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="AL5" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="AK5" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL5" s="12" t="s">
-        <v>101</v>
-      </c>
       <c r="AM5" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="AN5" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AO5" s="12" t="s">
         <v>102</v>
+      </c>
+      <c r="AN5" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="AO5" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="AP5" s="12" t="s">
         <v>103</v>
       </c>
       <c r="AQ5" s="12" t="s">
-        <v>60</v>
+        <v>104</v>
+      </c>
+      <c r="AR5" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G6" s="15" t="n">
         <v>45658</v>
@@ -2176,16 +2246,16 @@
         <v>46202</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P6" s="1" t="n">
         <v>0.373</v>
@@ -2195,96 +2265,99 @@
         <v>Growth 10-50%</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>108</v>
+        <v>59</v>
       </c>
       <c r="W6" s="1" t="s">
         <v>109</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="AA6" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD6" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="AC6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AE6" s="1" t="n">
         <v>0.568</v>
       </c>
-      <c r="AE6" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="AF6" s="1" t="s">
-        <v>66</v>
+        <v>111</v>
       </c>
       <c r="AG6" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AH6" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ6" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
+      </c>
+      <c r="AI6" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="AK6" s="1" t="s">
         <v>69</v>
       </c>
       <c r="AL6" s="1" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="AM6" s="1" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="AN6" s="1" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="AO6" s="1" t="s">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="AP6" s="1" t="s">
         <v>113</v>
       </c>
       <c r="AQ6" s="1" t="s">
-        <v>60</v>
+        <v>114</v>
+      </c>
+      <c r="AR6" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G7" s="15" t="n">
         <v>45658</v>
@@ -2300,16 +2373,16 @@
         <v>46202</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P7" s="1" t="n">
         <v>1.058</v>
@@ -2319,93 +2392,96 @@
         <v>Growth &gt;50%</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>108</v>
+        <v>59</v>
       </c>
       <c r="W7" s="1" t="s">
         <v>109</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="AE7" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AC7" s="1" t="s">
         <v>117</v>
       </c>
       <c r="AF7" s="1" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="AG7" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AH7" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ7" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
+      </c>
+      <c r="AI7" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="AK7" s="1" t="s">
         <v>69</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>71</v>
+        <v>119</v>
       </c>
       <c r="AN7" s="1" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>119</v>
+        <v>64</v>
       </c>
       <c r="AP7" s="1" t="s">
         <v>120</v>
       </c>
       <c r="AQ7" s="1" t="s">
-        <v>60</v>
+        <v>121</v>
+      </c>
+      <c r="AR7" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G8" s="15" t="n">
         <v>45658</v>
@@ -2421,16 +2497,16 @@
         <v>46202</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P8" s="1" t="n">
         <v>0.719</v>
@@ -2440,93 +2516,96 @@
         <v>Growth &gt;50%</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>123</v>
+        <v>59</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="X8" s="1" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="AA8" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE8" s="1" t="s">
-        <v>124</v>
+        <v>65</v>
+      </c>
+      <c r="AC8" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="AF8" s="1" t="s">
-        <v>66</v>
+        <v>125</v>
       </c>
       <c r="AG8" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AH8" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ8" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
+      </c>
+      <c r="AI8" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="AK8" s="1" t="s">
         <v>69</v>
       </c>
       <c r="AL8" s="1" t="s">
-        <v>125</v>
+        <v>70</v>
       </c>
       <c r="AM8" s="1" t="s">
-        <v>71</v>
+        <v>126</v>
       </c>
       <c r="AN8" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="AO8" s="1" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="AP8" s="1" t="s">
         <v>127</v>
       </c>
       <c r="AQ8" s="1" t="s">
-        <v>72</v>
+        <v>128</v>
+      </c>
+      <c r="AR8" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G9" s="15" t="n">
         <v>45658</v>
@@ -2542,16 +2621,16 @@
         <v>46202</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P9" s="14" t="n">
         <v>0.599</v>
@@ -2561,93 +2640,96 @@
         <v>Growth &gt;50%</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>108</v>
+        <v>59</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="X9" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Y9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA9" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="Y9" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z9" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA9" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="AB9" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE9" s="1" t="s">
-        <v>132</v>
+        <v>65</v>
+      </c>
+      <c r="AC9" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="AF9" s="1" t="s">
-        <v>66</v>
+        <v>133</v>
       </c>
       <c r="AG9" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AH9" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ9" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
+      </c>
+      <c r="AI9" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="AK9" s="1" t="s">
         <v>69</v>
       </c>
       <c r="AL9" s="1" t="s">
-        <v>133</v>
+        <v>70</v>
       </c>
       <c r="AM9" s="1" t="s">
         <v>134</v>
       </c>
       <c r="AN9" s="1" t="s">
-        <v>62</v>
+        <v>135</v>
       </c>
       <c r="AO9" s="1" t="s">
-        <v>135</v>
+        <v>64</v>
       </c>
       <c r="AP9" s="1" t="s">
         <v>136</v>
       </c>
       <c r="AQ9" s="1" t="s">
-        <v>60</v>
+        <v>137</v>
+      </c>
+      <c r="AR9" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G10" s="15" t="n">
         <v>45658</v>
@@ -2663,16 +2745,16 @@
         <v>46202</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P10" s="14" t="n">
         <v>0.28</v>
@@ -2682,93 +2764,96 @@
         <v>Growth 10-50%</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>108</v>
+        <v>59</v>
       </c>
       <c r="W10" s="1" t="s">
         <v>109</v>
       </c>
       <c r="X10" s="1" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="AA10" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB10" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE10" s="1" t="s">
-        <v>141</v>
+        <v>65</v>
+      </c>
+      <c r="AC10" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="AF10" s="1" t="s">
-        <v>66</v>
+        <v>142</v>
       </c>
       <c r="AG10" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AH10" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ10" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
+      </c>
+      <c r="AI10" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="AK10" s="1" t="s">
         <v>69</v>
       </c>
       <c r="AL10" s="1" t="s">
-        <v>142</v>
+        <v>70</v>
       </c>
       <c r="AM10" s="1" t="s">
         <v>143</v>
       </c>
       <c r="AN10" s="1" t="s">
-        <v>60</v>
+        <v>144</v>
       </c>
       <c r="AO10" s="1" t="s">
-        <v>144</v>
+        <v>62</v>
       </c>
       <c r="AP10" s="1" t="s">
         <v>145</v>
       </c>
       <c r="AQ10" s="1" t="s">
-        <v>62</v>
+        <v>146</v>
+      </c>
+      <c r="AR10" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G11" s="15" t="n">
         <v>45658</v>
@@ -2784,16 +2869,16 @@
         <v>46202</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P11" s="14" t="n">
         <v>0.36</v>
@@ -2803,93 +2888,96 @@
         <v>Growth 10-50%</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>108</v>
+        <v>59</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>151</v>
+        <v>109</v>
       </c>
       <c r="X11" s="1" t="s">
-        <v>62</v>
+        <v>152</v>
       </c>
       <c r="Y11" s="1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="AA11" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB11" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE11" s="1" t="s">
-        <v>152</v>
+        <v>65</v>
+      </c>
+      <c r="AC11" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="AF11" s="1" t="s">
-        <v>66</v>
+        <v>153</v>
       </c>
       <c r="AG11" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AH11" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ11" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
+      </c>
+      <c r="AI11" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="AK11" s="1" t="s">
         <v>69</v>
       </c>
       <c r="AL11" s="1" t="s">
-        <v>153</v>
+        <v>70</v>
       </c>
       <c r="AM11" s="1" t="s">
         <v>154</v>
       </c>
       <c r="AN11" s="1" t="s">
-        <v>72</v>
+        <v>155</v>
       </c>
       <c r="AO11" s="1" t="s">
-        <v>155</v>
+        <v>73</v>
       </c>
       <c r="AP11" s="1" t="s">
         <v>156</v>
       </c>
       <c r="AQ11" s="1" t="s">
-        <v>60</v>
+        <v>157</v>
+      </c>
+      <c r="AR11" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G12" s="15" t="n">
         <v>45658</v>
@@ -2905,16 +2993,16 @@
         <v>46202</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P12" s="14" t="n">
         <v>1.125</v>
@@ -2924,93 +3012,96 @@
         <v>Growth &gt;50%</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>108</v>
+        <v>59</v>
       </c>
       <c r="W12" s="1" t="s">
         <v>109</v>
       </c>
       <c r="X12" s="1" t="s">
-        <v>62</v>
+        <v>110</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>160</v>
+        <v>64</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>62</v>
+        <v>161</v>
       </c>
       <c r="AA12" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB12" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE12" s="1" t="s">
-        <v>161</v>
+        <v>65</v>
+      </c>
+      <c r="AC12" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="AF12" s="1" t="s">
-        <v>66</v>
+        <v>162</v>
       </c>
       <c r="AG12" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AH12" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ12" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
+      </c>
+      <c r="AI12" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="AK12" s="1" t="s">
         <v>69</v>
       </c>
       <c r="AL12" s="1" t="s">
-        <v>162</v>
+        <v>70</v>
       </c>
       <c r="AM12" s="1" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="AN12" s="1" t="s">
-        <v>60</v>
+        <v>155</v>
       </c>
       <c r="AO12" s="1" t="s">
-        <v>163</v>
+        <v>62</v>
       </c>
       <c r="AP12" s="1" t="s">
         <v>164</v>
       </c>
       <c r="AQ12" s="1" t="s">
-        <v>60</v>
+        <v>165</v>
+      </c>
+      <c r="AR12" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G13" s="15" t="n">
         <v>45658</v>
@@ -3026,16 +3117,16 @@
         <v>46202</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P13" s="14" t="n">
         <v>0.2678</v>
@@ -3045,96 +3136,99 @@
         <v>Growth 10-50%</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>108</v>
+        <v>59</v>
       </c>
       <c r="W13" s="1" t="s">
         <v>109</v>
       </c>
       <c r="X13" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="Y13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z13" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA13" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="Y13" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z13" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA13" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="AB13" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="AC13" s="1" t="n">
+        <v>99</v>
+      </c>
+      <c r="AC13" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AD13" s="1" t="n">
         <v>0.523</v>
       </c>
-      <c r="AE13" s="1" t="s">
-        <v>170</v>
-      </c>
       <c r="AF13" s="1" t="s">
-        <v>66</v>
+        <v>171</v>
       </c>
       <c r="AG13" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AH13" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ13" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
+      </c>
+      <c r="AI13" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="AK13" s="1" t="s">
         <v>69</v>
       </c>
       <c r="AL13" s="1" t="s">
-        <v>171</v>
+        <v>70</v>
       </c>
       <c r="AM13" s="1" t="s">
         <v>172</v>
       </c>
       <c r="AN13" s="1" t="s">
-        <v>62</v>
+        <v>173</v>
       </c>
       <c r="AO13" s="1" t="s">
-        <v>173</v>
+        <v>64</v>
       </c>
       <c r="AP13" s="1" t="s">
         <v>174</v>
       </c>
       <c r="AQ13" s="1" t="s">
-        <v>72</v>
+        <v>175</v>
+      </c>
+      <c r="AR13" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G14" s="15" t="n">
         <v>45658</v>
@@ -3150,16 +3244,16 @@
         <v>46202</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P14" s="14" t="n">
         <v>0.1985</v>
@@ -3169,96 +3263,99 @@
         <v>Growth 10-50%</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U14" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>123</v>
+        <v>59</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>180</v>
+        <v>124</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>60</v>
+        <v>181</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="Z14" s="1" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="AA14" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB14" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC14" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="AB14" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AC14" s="1" t="n">
+      <c r="AD14" s="1" t="n">
         <v>0.756</v>
       </c>
-      <c r="AE14" s="1" t="s">
-        <v>181</v>
-      </c>
       <c r="AF14" s="1" t="s">
-        <v>66</v>
+        <v>182</v>
       </c>
       <c r="AG14" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AH14" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ14" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
+      </c>
+      <c r="AI14" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="AK14" s="1" t="s">
         <v>69</v>
       </c>
       <c r="AL14" s="1" t="s">
-        <v>182</v>
+        <v>70</v>
       </c>
       <c r="AM14" s="1" t="s">
         <v>183</v>
       </c>
       <c r="AN14" s="1" t="s">
-        <v>72</v>
+        <v>184</v>
       </c>
       <c r="AO14" s="1" t="s">
-        <v>184</v>
+        <v>73</v>
       </c>
       <c r="AP14" s="1" t="s">
         <v>185</v>
       </c>
       <c r="AQ14" s="1" t="s">
-        <v>60</v>
+        <v>186</v>
+      </c>
+      <c r="AR14" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G15" s="15" t="n">
         <v>45658</v>
@@ -3274,16 +3371,16 @@
         <v>46202</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P15" s="14" t="n">
         <v>-0.4</v>
@@ -3293,90 +3390,93 @@
         <v>Decline 25-50%</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>108</v>
+        <v>59</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>192</v>
+        <v>109</v>
       </c>
       <c r="X15" s="1" t="s">
-        <v>60</v>
+        <v>193</v>
       </c>
       <c r="Y15" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="AA15" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AB15" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE15" s="1" t="s">
-        <v>193</v>
+        <v>65</v>
+      </c>
+      <c r="AC15" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="AF15" s="1" t="s">
-        <v>66</v>
+        <v>194</v>
       </c>
       <c r="AG15" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AH15" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ15" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
+      </c>
+      <c r="AI15" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="AK15" s="1" t="s">
         <v>69</v>
       </c>
       <c r="AL15" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="AN15" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
+      </c>
+      <c r="AM15" s="1" t="s">
+        <v>195</v>
       </c>
       <c r="AO15" s="1" t="s">
-        <v>195</v>
+        <v>64</v>
       </c>
       <c r="AP15" s="1" t="s">
         <v>196</v>
       </c>
       <c r="AQ15" s="1" t="s">
-        <v>60</v>
+        <v>197</v>
+      </c>
+      <c r="AR15" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G16" s="15" t="n">
         <v>45658</v>
@@ -3392,16 +3492,16 @@
         <v>46202</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P16" s="14" t="n">
         <v>0.603</v>
@@ -3411,93 +3511,96 @@
         <v>Growth &gt;50%</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>108</v>
+        <v>59</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>201</v>
+        <v>109</v>
       </c>
       <c r="X16" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="Y16" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA16" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="Y16" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z16" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA16" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="AB16" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="AE16" s="1" t="s">
-        <v>202</v>
+        <v>99</v>
+      </c>
+      <c r="AC16" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="AF16" s="1" t="s">
-        <v>66</v>
+        <v>203</v>
       </c>
       <c r="AG16" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AH16" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ16" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
+      </c>
+      <c r="AI16" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="AK16" s="1" t="s">
         <v>69</v>
       </c>
       <c r="AL16" s="1" t="s">
-        <v>203</v>
+        <v>70</v>
       </c>
       <c r="AM16" s="1" t="s">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="AN16" s="1" t="s">
-        <v>62</v>
+        <v>173</v>
       </c>
       <c r="AO16" s="1" t="s">
-        <v>204</v>
+        <v>64</v>
       </c>
       <c r="AP16" s="1" t="s">
         <v>205</v>
       </c>
       <c r="AQ16" s="1" t="s">
-        <v>62</v>
+        <v>206</v>
+      </c>
+      <c r="AR16" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G17" s="15" t="n">
         <v>45658</v>
@@ -3513,16 +3616,16 @@
         <v>46202</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P17" s="14" t="n">
         <v>1.314</v>
@@ -3532,93 +3635,96 @@
         <v>Growth &gt;50%</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V17" s="1" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>211</v>
+        <v>85</v>
       </c>
       <c r="X17" s="1" t="s">
-        <v>62</v>
+        <v>212</v>
       </c>
       <c r="Y17" s="1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="Z17" s="1" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="AA17" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="AB17" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE17" s="1" t="s">
-        <v>212</v>
+        <v>65</v>
+      </c>
+      <c r="AC17" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="AF17" s="1" t="s">
-        <v>66</v>
+        <v>213</v>
       </c>
       <c r="AG17" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AH17" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ17" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
+      </c>
+      <c r="AI17" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="AK17" s="1" t="s">
         <v>69</v>
       </c>
       <c r="AL17" s="1" t="s">
-        <v>213</v>
+        <v>70</v>
       </c>
       <c r="AM17" s="1" t="s">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="AN17" s="1" t="s">
-        <v>62</v>
+        <v>184</v>
       </c>
       <c r="AO17" s="1" t="s">
-        <v>214</v>
+        <v>64</v>
       </c>
       <c r="AP17" s="1" t="s">
         <v>215</v>
       </c>
       <c r="AQ17" s="1" t="s">
-        <v>60</v>
+        <v>216</v>
+      </c>
+      <c r="AR17" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G18" s="15" t="n">
         <v>45658</v>
@@ -3634,16 +3740,16 @@
         <v>46202</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P18" s="14" t="n">
         <v>1.858</v>
@@ -3653,90 +3759,93 @@
         <v>Growth &gt;50%</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V18" s="1" t="s">
-        <v>108</v>
+        <v>59</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="X18" s="1" t="s">
-        <v>60</v>
+        <v>222</v>
       </c>
       <c r="Y18" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z18" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="AA18" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AB18" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE18" s="1" t="s">
-        <v>222</v>
+        <v>65</v>
+      </c>
+      <c r="AC18" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="AF18" s="1" t="s">
-        <v>66</v>
+        <v>223</v>
       </c>
       <c r="AG18" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AH18" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ18" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
+      </c>
+      <c r="AI18" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="AK18" s="1" t="s">
         <v>69</v>
       </c>
       <c r="AL18" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="AN18" s="1" t="s">
-        <v>60</v>
+        <v>70</v>
+      </c>
+      <c r="AM18" s="1" t="s">
+        <v>224</v>
       </c>
       <c r="AO18" s="1" t="s">
-        <v>224</v>
+        <v>62</v>
       </c>
       <c r="AP18" s="1" t="s">
         <v>225</v>
       </c>
       <c r="AQ18" s="1" t="s">
-        <v>72</v>
+        <v>226</v>
+      </c>
+      <c r="AR18" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G19" s="15" t="n">
         <v>45778</v>
@@ -3755,58 +3864,58 @@
         <v>46234</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="V19" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>236</v>
+        <v>60</v>
       </c>
       <c r="X19" s="1" t="s">
-        <v>60</v>
+        <v>237</v>
       </c>
       <c r="Y19" s="1" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="Z19" s="1" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="AA19" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB19" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="AC19" s="1" t="s">
-        <v>237</v>
+        <v>65</v>
       </c>
       <c r="AD19" s="1" t="s">
         <v>238</v>
@@ -3815,16 +3924,16 @@
         <v>239</v>
       </c>
       <c r="AF19" s="1" t="s">
-        <v>66</v>
+        <v>240</v>
       </c>
       <c r="AG19" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AH19" s="1" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="AI19" s="1" t="s">
-        <v>240</v>
+        <v>59</v>
       </c>
       <c r="AJ19" s="1" t="s">
         <v>241</v>
@@ -3836,69 +3945,72 @@
         <v>243</v>
       </c>
       <c r="AM19" s="1" t="s">
-        <v>57</v>
+        <v>244</v>
       </c>
       <c r="AN19" s="1" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="AO19" s="1" t="s">
-        <v>244</v>
+        <v>73</v>
       </c>
       <c r="AP19" s="1" t="s">
         <v>245</v>
       </c>
       <c r="AQ19" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>246</v>
+      </c>
+      <c r="AR19" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G20" s="16" t="n">
+        <v>94</v>
+      </c>
+      <c r="G20" s="15" t="n">
         <v>45658</v>
       </c>
-      <c r="H20" s="16" t="n">
+      <c r="H20" s="15" t="n">
         <v>46174</v>
       </c>
       <c r="I20" s="1" t="n">
         <f aca="false">IF(AND(G20&lt;&gt;"",H20&lt;&gt;""),(YEAR(H20)-YEAR(G20))*12+(MONTH(H20)-MONTH(G20)),"")</f>
         <v>17</v>
       </c>
-      <c r="J20" s="16" t="n">
+      <c r="J20" s="15" t="n">
         <v>46237</v>
       </c>
-      <c r="K20" s="16" t="n">
+      <c r="K20" s="15" t="n">
         <v>46237</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P20" s="17" t="n">
+        <v>54</v>
+      </c>
+      <c r="P20" s="14" t="n">
         <v>0.357</v>
       </c>
       <c r="Q20" s="1" t="str">
@@ -3906,70 +4018,70 @@
         <v>Growth 10-50%</v>
       </c>
       <c r="R20" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="V20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="W20" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="X20" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y20" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z20" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA20" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB20" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AC20" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD20" s="14" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="AE20" s="14" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AF20" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="AG20" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AH20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AI20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AK20" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AL20" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AM20" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="AO20" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="S20" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="T20" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="U20" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="V20" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="W20" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="X20" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="Y20" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z20" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA20" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AB20" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC20" s="17" t="n">
-        <v>1.286</v>
-      </c>
-      <c r="AD20" s="17" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="AE20" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="AF20" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AG20" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AH20" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ20" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AK20" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="AL20" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="AN20" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AO20" s="1" t="s">
-        <v>252</v>
       </c>
       <c r="AP20" s="1" t="s">
         <v>253</v>
@@ -3977,55 +4089,58 @@
       <c r="AQ20" s="1" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AR20" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G21" s="18" t="n">
+        <v>50</v>
+      </c>
+      <c r="G21" s="16" t="n">
         <v>45658</v>
       </c>
-      <c r="H21" s="18" t="n">
+      <c r="H21" s="16" t="n">
         <v>46174</v>
       </c>
       <c r="I21" s="1" t="n">
         <f aca="false">IF(AND(G21&lt;&gt;"",H21&lt;&gt;""),(YEAR(H21)-YEAR(G21))*12+(MONTH(H21)-MONTH(G21)),"")</f>
         <v>17</v>
       </c>
-      <c r="J21" s="18" t="n">
+      <c r="J21" s="16" t="n">
         <v>46238</v>
       </c>
-      <c r="K21" s="18" t="n">
+      <c r="K21" s="16" t="n">
         <v>46238</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P21" s="17" t="n">
+        <v>54</v>
+      </c>
+      <c r="P21" s="14" t="n">
         <v>0.263</v>
       </c>
       <c r="Q21" s="1" t="str">
@@ -4033,46 +4148,46 @@
         <v>Growth 10-50%</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="V21" s="1" t="s">
-        <v>249</v>
+        <v>59</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="X21" s="1" t="s">
-        <v>60</v>
+        <v>262</v>
       </c>
       <c r="Y21" s="1" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="Z21" s="1" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="AA21" s="1" t="s">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="AB21" s="1" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AC21" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="AD21" s="17" t="n">
+        <v>117</v>
+      </c>
+      <c r="AD21" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="AE21" s="14" t="n">
         <v>0.627</v>
-      </c>
-      <c r="AE21" s="1" t="s">
-        <v>263</v>
       </c>
       <c r="AF21" s="1" t="s">
         <v>264</v>
@@ -4081,34 +4196,173 @@
         <v>265</v>
       </c>
       <c r="AH21" s="1" t="s">
-        <v>62</v>
+        <v>266</v>
       </c>
       <c r="AI21" s="1" t="s">
-        <v>266</v>
+        <v>64</v>
       </c>
       <c r="AJ21" s="1" t="s">
-        <v>68</v>
+        <v>267</v>
       </c>
       <c r="AK21" s="1" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="AL21" s="1" t="s">
-        <v>267</v>
+        <v>99</v>
       </c>
       <c r="AM21" s="1" t="s">
         <v>268</v>
       </c>
       <c r="AN21" s="1" t="s">
-        <v>62</v>
+        <v>269</v>
       </c>
       <c r="AO21" s="1" t="s">
-        <v>269</v>
+        <v>64</v>
       </c>
       <c r="AP21" s="1" t="s">
         <v>270</v>
       </c>
       <c r="AQ21" s="1" t="s">
         <v>271</v>
+      </c>
+      <c r="AR21" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G22" s="15" t="n">
+        <v>45505</v>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I22" s="1" t="n">
+        <f aca="false">IF(AND(G22&lt;&gt;"",H22&lt;&gt;""),(YEAR(H22)-YEAR(G22))*12+(MONTH(H22)-MONTH(G22)),"")</f>
+        <v>24</v>
+      </c>
+      <c r="J22" s="15" t="n">
+        <v>46240</v>
+      </c>
+      <c r="K22" s="15" t="n">
+        <v>46240</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="P22" s="1" t="n">
+        <v>1.026</v>
+      </c>
+      <c r="Q22" s="1" t="str">
+        <f aca="false">IF(P22="","",IF(P22&gt;0.5,"Growth &gt;50%",IF(P22&gt;0.1,"Growth 10-50%",IF(P22&gt;=-0.1,"Flat",IF(P22&gt;=-0.25,"Decline 10-25%",IF(P22&gt;=-0.5,"Decline 25-50%",IF(P22&gt;=-0.75,"Decline 50-75%","Decline &gt;75%")))))))</f>
+        <v>Growth &gt;50%</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="V22" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="W22" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="X22" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="Y22" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z22" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA22" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="AB22" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AC22" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AD22" s="1" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="AE22" s="1" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="AF22" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="AG22" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="AH22" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AI22" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ22" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="AK22" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AL22" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AM22" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="AN22" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="AO22" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AP22" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="AQ22" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="AR22" s="1" t="s">
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -4140,312 +4394,312 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
-        <v>272</v>
+      <c r="A1" s="17" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
-        <v>273</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>274</v>
+      <c r="A2" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="23" t="s">
-        <v>275</v>
+      <c r="B3" s="21" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="23" t="s">
-        <v>276</v>
+      <c r="B4" s="21" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="23" t="s">
-        <v>277</v>
+      <c r="B5" s="21" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="23" t="s">
-        <v>278</v>
+      <c r="B6" s="21" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="22" t="s">
-        <v>279</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>280</v>
+      <c r="A7" s="20" t="s">
+        <v>301</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="23" t="s">
-        <v>281</v>
+      <c r="B8" s="21" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="23" t="s">
-        <v>282</v>
+      <c r="B9" s="21" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="23" t="s">
-        <v>283</v>
+      <c r="B10" s="21" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="23" t="s">
-        <v>284</v>
+      <c r="B11" s="21" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="23" t="s">
-        <v>285</v>
+      <c r="B12" s="21" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="23" t="s">
-        <v>286</v>
+      <c r="B13" s="21" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="23" t="s">
-        <v>287</v>
+      <c r="B14" s="21" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="23" t="s">
-        <v>288</v>
+      <c r="B15" s="21" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="23" t="s">
-        <v>289</v>
+      <c r="B16" s="21" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>290</v>
+      <c r="A17" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="23" t="s">
-        <v>291</v>
+      <c r="A18" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="23" t="s">
-        <v>292</v>
+      <c r="A19" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="23" t="s">
-        <v>293</v>
+      <c r="A20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="23" t="s">
-        <v>294</v>
+      <c r="A21" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>295</v>
+        <v>317</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>296</v>
+        <v>318</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" s="23" t="s">
-        <v>297</v>
+      <c r="A24" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="23" t="s">
-        <v>298</v>
+      <c r="A25" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26" s="23" t="s">
-        <v>299</v>
+      <c r="A26" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>300</v>
+      <c r="A27" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="B28" s="23" t="s">
-        <v>301</v>
+      <c r="A28" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="22" t="s">
-        <v>302</v>
-      </c>
-      <c r="B29" s="23" t="s">
-        <v>303</v>
+      <c r="A29" s="20" t="s">
+        <v>324</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="23" t="s">
-        <v>304</v>
+      <c r="A30" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" s="23" t="s">
-        <v>305</v>
+      <c r="A31" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="B32" s="23" t="s">
-        <v>306</v>
+      <c r="A32" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" s="23" t="s">
-        <v>307</v>
+      <c r="A33" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="21" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>308</v>
+        <v>330</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35" s="23" t="s">
-        <v>309</v>
+      <c r="A35" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="21" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>310</v>
+        <v>332</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="B37" s="23" t="s">
-        <v>311</v>
+      <c r="A37" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" s="21" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B38" s="23" t="s">
-        <v>312</v>
+      <c r="A38" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" s="21" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="22" t="s">
-        <v>313</v>
-      </c>
-      <c r="B39" s="23" t="s">
-        <v>314</v>
+      <c r="A39" s="20" t="s">
+        <v>335</v>
+      </c>
+      <c r="B39" s="21" t="s">
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -4473,106 +4727,106 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
-        <v>315</v>
+      <c r="A1" s="17" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
-        <v>316</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>317</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>318</v>
+      <c r="A2" s="19" t="s">
+        <v>338</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>339</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>319</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>320</v>
+      <c r="A3" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="23" t="s">
-        <v>150</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>321</v>
-      </c>
-      <c r="C4" s="23"/>
+      <c r="A4" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>343</v>
+      </c>
+      <c r="C4" s="21"/>
     </row>
     <row r="5" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>322</v>
-      </c>
-      <c r="C5" s="23"/>
+      <c r="A5" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="C5" s="21"/>
     </row>
     <row r="6" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="23" t="s">
-        <v>323</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>324</v>
-      </c>
-      <c r="C6" s="23"/>
+      <c r="A6" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>346</v>
+      </c>
+      <c r="C6" s="21"/>
     </row>
     <row r="7" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>325</v>
-      </c>
-      <c r="C7" s="23"/>
+      <c r="A7" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="C7" s="21"/>
     </row>
     <row r="8" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>326</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>327</v>
+      <c r="A8" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>348</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="23" t="s">
-        <v>328</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>329</v>
-      </c>
-      <c r="C9" s="23"/>
+      <c r="A9" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>351</v>
+      </c>
+      <c r="C9" s="21"/>
     </row>
     <row r="10" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>330</v>
-      </c>
-      <c r="C10" s="23"/>
+      <c r="A10" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="C10" s="21"/>
     </row>
     <row r="11" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="23" t="s">
-        <v>259</v>
-      </c>
-      <c r="B11" s="23" t="s">
-        <v>331</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>332</v>
+      <c r="A11" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>354</v>
       </c>
     </row>
   </sheetData>
